--- a/AAAGameData/DataTables/SpecialEffectTable.xlsx
+++ b/AAAGameData/DataTables/SpecialEffectTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15300"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="144">
   <si>
     <t>#</t>
   </si>
@@ -68,6 +68,9 @@
     <t>Weight</t>
   </si>
   <si>
+    <t>EffectParams</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -89,7 +92,7 @@
     <t>效果名称</t>
   </si>
   <si>
-    <t>效果分类：1=玩家先手,2=敌人先手,3=玩家偷袭</t>
+    <t>效果分类：0=消耗品,1=玩家先手,2=敌人先手,3=玩家偷袭</t>
   </si>
   <si>
     <t>效果类型：1=增益,2=减益,3=控制</t>
@@ -116,6 +119,9 @@
     <t>随机权重</t>
   </si>
   <si>
+    <t>效果参数（JSON格式）</t>
+  </si>
+  <si>
     <t>玩家先手·速度爆发</t>
   </si>
   <si>
@@ -183,6 +189,276 @@
   </si>
   <si>
     <t>3003</t>
+  </si>
+  <si>
+    <t>消耗品·随机金币</t>
+  </si>
+  <si>
+    <t>使用后随机获得100-500金币</t>
+  </si>
+  <si>
+    <t>{"type":"AddGold","min":100,"max":500}</t>
+  </si>
+  <si>
+    <t>消耗品·恢复生命值</t>
+  </si>
+  <si>
+    <t>使用后恢复500点生命值</t>
+  </si>
+  <si>
+    <t>{"type":"RestoreHP","value":500}</t>
+  </si>
+  <si>
+    <t>消耗品·恢复魔法值</t>
+  </si>
+  <si>
+    <t>使用后恢复300点魔法值</t>
+  </si>
+  <si>
+    <t>{"type":"RestoreMP","value":300}</t>
+  </si>
+  <si>
+    <t>消耗品·获得经验值</t>
+  </si>
+  <si>
+    <t>使用后获得1000点经验值</t>
+  </si>
+  <si>
+    <t>{"type":"AddExp","value":1000}</t>
+  </si>
+  <si>
+    <t>解锁神圣庇护</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：神圣庇护</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1001}</t>
+  </si>
+  <si>
+    <t>解锁烈焰风暴</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：烈焰风暴</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1002}</t>
+  </si>
+  <si>
+    <t>解锁时间回溯</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：时间回溯</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1003}</t>
+  </si>
+  <si>
+    <t>解锁战争号角</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：战争号角</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1004}</t>
+  </si>
+  <si>
+    <t>解锁暗影突袭</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：暗影突袭</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1005}</t>
+  </si>
+  <si>
+    <t>解锁生命汲取</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：生命汲取</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1006}</t>
+  </si>
+  <si>
+    <t>解锁冰霜新星</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：冰霜新星</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1007}</t>
+  </si>
+  <si>
+    <t>解锁狂暴</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：狂暴</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1008}</t>
+  </si>
+  <si>
+    <t>解锁群体治疗</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：群体治疗</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1009}</t>
+  </si>
+  <si>
+    <t>解锁雷霆一击</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：雷霆一击</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1010}</t>
+  </si>
+  <si>
+    <t>解锁混乱诅咒</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：混乱诅咒</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1011}</t>
+  </si>
+  <si>
+    <t>解锁不屈意志</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：不屈意志</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1012}</t>
+  </si>
+  <si>
+    <t>解锁反伤之盾</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：反伤之盾</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1013}</t>
+  </si>
+  <si>
+    <t>解锁圣域防线</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：圣域防线</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1014}</t>
+  </si>
+  <si>
+    <t>解锁护盾再生</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：护盾再生</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1015}</t>
+  </si>
+  <si>
+    <t>解锁救赎之光</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：救赎之光</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1016}</t>
+  </si>
+  <si>
+    <t>解锁血源强化</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：血源强化</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1017}</t>
+  </si>
+  <si>
+    <t>解锁吸血之刃</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：吸血之刃</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1018}</t>
+  </si>
+  <si>
+    <t>解锁灾厄之雷</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：灾厄之雷</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1019}</t>
+  </si>
+  <si>
+    <t>解锁护甲破碎</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：护甲破碎</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1020}</t>
+  </si>
+  <si>
+    <t>解锁虚弱诅咒</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：虚弱诅咒</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1021}</t>
+  </si>
+  <si>
+    <t>解锁沉默之符</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：沉默之符</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1022}</t>
+  </si>
+  <si>
+    <t>解锁嘲讽之声</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：嘲讽之声</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1023}</t>
+  </si>
+  <si>
+    <t>解锁剧毒之雾</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：剧毒之雾</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1024}</t>
+  </si>
+  <si>
+    <t>解锁伤害转移</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：伤害转移</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1025}</t>
+  </si>
+  <si>
+    <t>解锁绝对零度</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：绝对零度</t>
+  </si>
+  <si>
+    <t>{"type":"UnlockCard","cardId":1026}</t>
   </si>
 </sst>
 </file>
@@ -195,7 +471,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -651,165 +934,158 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1157,464 +1433,1574 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:N43"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="44" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32" style="1" customWidth="1"/>
-    <col min="7" max="7" width="44" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24" style="1" customWidth="1"/>
-    <col min="9" max="9" width="30" style="1" customWidth="1"/>
-    <col min="10" max="10" width="27" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12" style="1" customWidth="1"/>
-    <col min="12" max="12" width="37" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="7" max="7" width="44" customWidth="1"/>
+    <col min="8" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="27" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="37" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="H4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="J4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="K4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="L4" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:13">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+      <c r="M4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:14">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
         <v>101</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K5">
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="1">
         <v>10001</v>
       </c>
-      <c r="L5" s="3">
-        <v>1</v>
-      </c>
-      <c r="M5" s="3">
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:13">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:14">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>102</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>10002</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>100</v>
+      </c>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:14">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
+        <v>103</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>10003</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>80</v>
+      </c>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:14">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
+        <v>201</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K6">
+      <c r="J8" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>10001</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
+        <v>100</v>
+      </c>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:14">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
+        <v>202</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K9" s="1">
         <v>10002</v>
       </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3">
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:13">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:14">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
+        <v>203</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>10004</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1">
+        <v>90</v>
+      </c>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:14">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
+        <v>301</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>10101</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
+        <v>100</v>
+      </c>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:14">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
+        <v>302</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>10102</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>100</v>
+      </c>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:14">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
+        <v>303</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>10103</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>80</v>
+      </c>
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:14">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:14">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:14">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:14">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:14">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:14">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1">
+        <v>2002</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:14">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1">
+        <v>2003</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:14">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1">
+        <v>2004</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:14">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1">
+        <v>2005</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:14">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1">
+        <v>2006</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:14">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1">
+        <v>2007</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:14">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1">
+        <v>2008</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:14">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1">
+        <v>2009</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:14">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1">
+        <v>2010</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:14">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1">
+        <v>2011</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:14">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1">
+        <v>2012</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:14">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1">
+        <v>2013</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K7">
-        <v>10003</v>
-      </c>
-      <c r="L7" s="3">
-        <v>1</v>
-      </c>
-      <c r="M7" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:13">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <v>201</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K8">
-        <v>10001</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1</v>
-      </c>
-      <c r="M8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:13">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
-        <v>202</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K9">
-        <v>10002</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1</v>
-      </c>
-      <c r="M9" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:13">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2">
-        <v>203</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K10">
-        <v>10004</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1</v>
-      </c>
-      <c r="M10" s="3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:13">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2">
-        <v>301</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3</v>
-      </c>
-      <c r="F11" s="3">
-        <v>2</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K11">
-        <v>10101</v>
-      </c>
-      <c r="L11" s="3">
-        <v>1</v>
-      </c>
-      <c r="M11" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:13">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2">
-        <v>302</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="3">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K12">
-        <v>10102</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:13">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2">
-        <v>303</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="3">
-        <v>3</v>
-      </c>
-      <c r="F13" s="3">
-        <v>2</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J13" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K13">
-        <v>10103</v>
-      </c>
-      <c r="L13" s="3">
-        <v>1</v>
-      </c>
-      <c r="M13" s="3">
-        <v>80</v>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:14">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1">
+        <v>2014</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:14">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:14">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="1:14">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>1</v>
+      </c>
+      <c r="M34" s="1">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="1:14">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>1</v>
+      </c>
+      <c r="M35" s="1">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="1:14">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:14">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" spans="1:14">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
+        <v>1</v>
+      </c>
+      <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:14">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" spans="1:14">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>1</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" spans="1:14">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>1</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" spans="1:14">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>1</v>
+      </c>
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" spans="1:14">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SpecialEffectTable.xlsx
+++ b/AAAGameData/DataTables/SpecialEffectTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="140">
   <si>
     <t>#</t>
   </si>
@@ -41,9 +41,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>EffectCategory</t>
-  </si>
-  <si>
     <t>EffectType</t>
   </si>
   <si>
@@ -62,9 +59,6 @@
     <t>IconId</t>
   </si>
   <si>
-    <t>Rarity</t>
-  </si>
-  <si>
     <t>Weight</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
     <t>效果名称</t>
   </si>
   <si>
-    <t>效果分类：0=消耗品,1=玩家先手,2=敌人先手,3=玩家偷袭</t>
-  </si>
-  <si>
     <t>效果类型：1=增益,2=减益,3=控制</t>
   </si>
   <si>
@@ -111,9 +102,6 @@
   </si>
   <si>
     <t>图标资源ID</t>
-  </si>
-  <si>
-    <t>稀有度：1=普通,2=罕见,3=稀有,4=传奇</t>
   </si>
   <si>
     <t>随机权重</t>
@@ -471,14 +459,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -934,148 +915,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1433,25 +1414,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="6" width="32" customWidth="1"/>
-    <col min="7" max="7" width="44" customWidth="1"/>
-    <col min="8" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="27" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="37" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="40" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="7" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="27" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1462,16 +1441,14 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1488,13 +1465,13 @@
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -1506,1501 +1483,1249 @@
       <c r="L2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:14">
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>101</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
-        <v>33</v>
+      <c r="F5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="1">
+        <v>-1</v>
       </c>
       <c r="J5" s="1">
-        <v>-1</v>
+        <v>10001</v>
       </c>
       <c r="K5" s="1">
-        <v>10001</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
         <v>100</v>
       </c>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:14">
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:12">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>102</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>36</v>
+      <c r="F6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="1">
+        <v>-1</v>
       </c>
       <c r="J6" s="1">
-        <v>-1</v>
+        <v>10002</v>
       </c>
       <c r="K6" s="1">
-        <v>10002</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1">
         <v>100</v>
       </c>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:14">
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:12">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>103</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
-        <v>39</v>
+      <c r="F7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="1">
+        <v>-1</v>
       </c>
       <c r="J7" s="1">
-        <v>-1</v>
+        <v>10003</v>
       </c>
       <c r="K7" s="1">
-        <v>10003</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1">
         <v>80</v>
       </c>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:14">
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:12">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>201</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2" t="s">
-        <v>33</v>
+      <c r="F8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="1">
+        <v>-1</v>
       </c>
       <c r="J8" s="1">
-        <v>-1</v>
+        <v>10001</v>
       </c>
       <c r="K8" s="1">
-        <v>10001</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1</v>
-      </c>
-      <c r="M8" s="1">
         <v>100</v>
       </c>
-      <c r="N8" s="1"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:14">
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:12">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>202</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E9" s="1">
-        <v>2</v>
-      </c>
-      <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2" t="s">
-        <v>36</v>
+      <c r="F9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="1">
+        <v>-1</v>
       </c>
       <c r="J9" s="1">
-        <v>-1</v>
+        <v>10002</v>
       </c>
       <c r="K9" s="1">
-        <v>10002</v>
-      </c>
-      <c r="L9" s="1">
-        <v>1</v>
-      </c>
-      <c r="M9" s="1">
         <v>100</v>
       </c>
-      <c r="N9" s="1"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:14">
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:12">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>203</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2" t="s">
-        <v>44</v>
+      <c r="F10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-1</v>
       </c>
       <c r="J10" s="1">
-        <v>-1</v>
+        <v>10004</v>
       </c>
       <c r="K10" s="1">
-        <v>10004</v>
-      </c>
-      <c r="L10" s="1">
-        <v>1</v>
-      </c>
-      <c r="M10" s="1">
         <v>90</v>
       </c>
-      <c r="N10" s="1"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:14">
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:12">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>301</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E11" s="1">
-        <v>3</v>
-      </c>
-      <c r="F11" s="1">
         <v>2</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="2"/>
+      <c r="F11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="1">
+        <v>-1</v>
+      </c>
       <c r="J11" s="1">
-        <v>-1</v>
+        <v>10101</v>
       </c>
       <c r="K11" s="1">
-        <v>10101</v>
-      </c>
-      <c r="L11" s="1">
-        <v>1</v>
-      </c>
-      <c r="M11" s="1">
         <v>100</v>
       </c>
-      <c r="N11" s="1"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:14">
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:12">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>302</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
       </c>
-      <c r="F12" s="1">
-        <v>3</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I12" s="2"/>
+      <c r="F12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="1">
+        <v>-1</v>
+      </c>
       <c r="J12" s="1">
-        <v>-1</v>
+        <v>10102</v>
       </c>
       <c r="K12" s="1">
-        <v>10102</v>
-      </c>
-      <c r="L12" s="1">
-        <v>1</v>
-      </c>
-      <c r="M12" s="1">
         <v>100</v>
       </c>
-      <c r="N12" s="1"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:14">
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:12">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>303</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E13" s="1">
-        <v>3</v>
-      </c>
-      <c r="F13" s="1">
         <v>2</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="2"/>
+      <c r="F13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="1">
+        <v>-1</v>
+      </c>
       <c r="J13" s="1">
-        <v>-1</v>
+        <v>10103</v>
       </c>
       <c r="K13" s="1">
-        <v>10103</v>
-      </c>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
-      <c r="M13" s="1">
         <v>80</v>
       </c>
-      <c r="N13" s="1"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="1:14">
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:12">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>1001</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="F14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="I14" s="1">
+        <v>-1</v>
+      </c>
       <c r="J14" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
       </c>
-      <c r="L14" s="1">
-        <v>1</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:14">
+      <c r="L14" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:12">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>1002</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="F15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+      <c r="I15" s="1">
+        <v>-1</v>
+      </c>
       <c r="J15" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
       </c>
-      <c r="L15" s="1">
-        <v>1</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:14">
+      <c r="L15" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:12">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>1003</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="F16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
+      <c r="I16" s="1">
+        <v>-1</v>
+      </c>
       <c r="J16" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
       </c>
-      <c r="L16" s="1">
-        <v>1</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" spans="1:14">
+      <c r="L16" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:12">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>1004</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="F17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
+      <c r="I17" s="1">
+        <v>-1</v>
+      </c>
       <c r="J17" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
       </c>
-      <c r="L17" s="1">
-        <v>1</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:14">
+      <c r="L17" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:12">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>2001</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>67</v>
-      </c>
+      <c r="F18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+      <c r="I18" s="1">
+        <v>-1</v>
+      </c>
       <c r="J18" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
       </c>
-      <c r="L18" s="1">
-        <v>1</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" spans="1:14">
+      <c r="L18" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:12">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>2002</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="F19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="I19" s="1">
+        <v>-1</v>
+      </c>
       <c r="J19" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
       </c>
-      <c r="L19" s="1">
-        <v>1</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:14">
+      <c r="L19" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:12">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>2003</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
       </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="F20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
+      <c r="I20" s="1">
+        <v>-1</v>
+      </c>
       <c r="J20" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
       </c>
-      <c r="L20" s="1">
-        <v>1</v>
-      </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="1:14">
+      <c r="L20" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:12">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>2004</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="F21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+      <c r="I21" s="1">
+        <v>-1</v>
+      </c>
       <c r="J21" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
       </c>
-      <c r="L21" s="1">
-        <v>1</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:14">
+      <c r="L21" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:12">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>2005</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="F22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
+      <c r="I22" s="1">
+        <v>-1</v>
+      </c>
       <c r="J22" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
         <v>0</v>
       </c>
-      <c r="L22" s="1">
-        <v>1</v>
-      </c>
-      <c r="M22" s="1">
-        <v>0</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" spans="1:14">
+      <c r="L22" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:12">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>2006</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="F23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="2"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="I23" s="1">
+        <v>-1</v>
+      </c>
       <c r="J23" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
       </c>
-      <c r="L23" s="1">
-        <v>1</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:14">
+      <c r="L23" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:12">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>2007</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
+      <c r="I24" s="1">
+        <v>-1</v>
+      </c>
       <c r="J24" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
       </c>
-      <c r="L24" s="1">
-        <v>1</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:14">
+      <c r="L24" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:12">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>2008</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>88</v>
-      </c>
+      <c r="F25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="I25" s="1">
+        <v>-1</v>
+      </c>
       <c r="J25" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
       </c>
-      <c r="L25" s="1">
-        <v>1</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="1:14">
+      <c r="L25" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:12">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>2009</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="F26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+      <c r="I26" s="1">
+        <v>-1</v>
+      </c>
       <c r="J26" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
         <v>0</v>
       </c>
-      <c r="L26" s="1">
-        <v>1</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:14">
+      <c r="L26" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:12">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>2010</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="F27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+      <c r="I27" s="1">
+        <v>-1</v>
+      </c>
       <c r="J27" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
         <v>0</v>
       </c>
-      <c r="L27" s="1">
-        <v>1</v>
-      </c>
-      <c r="M27" s="1">
-        <v>0</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="1:14">
+      <c r="L27" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:12">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>2011</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
       </c>
-      <c r="F28" s="1">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="F28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+      <c r="I28" s="1">
+        <v>-1</v>
+      </c>
       <c r="J28" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
       </c>
-      <c r="L28" s="1">
-        <v>1</v>
-      </c>
-      <c r="M28" s="1">
-        <v>0</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="1:14">
+      <c r="L28" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:12">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>2012</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
-      <c r="F29" s="1">
-        <v>0</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="F29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
+      <c r="I29" s="1">
+        <v>-1</v>
+      </c>
       <c r="J29" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
         <v>0</v>
       </c>
-      <c r="L29" s="1">
-        <v>1</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" spans="1:14">
+      <c r="L29" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:12">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>2013</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
       </c>
-      <c r="F30" s="1">
-        <v>0</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="F30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+      <c r="I30" s="1">
+        <v>-1</v>
+      </c>
       <c r="J30" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
       </c>
-      <c r="L30" s="1">
-        <v>1</v>
-      </c>
-      <c r="M30" s="1">
-        <v>0</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" spans="1:14">
+      <c r="L30" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:12">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>2014</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
-      <c r="F31" s="1">
-        <v>0</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>106</v>
-      </c>
+      <c r="F31" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
+      <c r="I31" s="1">
+        <v>-1</v>
+      </c>
       <c r="J31" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
       </c>
-      <c r="L31" s="1">
-        <v>1</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" spans="1:14">
+      <c r="L31" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:12">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>2015</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
       </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>109</v>
-      </c>
+      <c r="F32" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
+      <c r="I32" s="1">
+        <v>-1</v>
+      </c>
       <c r="J32" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
       </c>
-      <c r="L32" s="1">
-        <v>1</v>
-      </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" spans="1:14">
+      <c r="L32" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:12">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>2016</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E33" s="1">
         <v>0</v>
       </c>
-      <c r="F33" s="1">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>112</v>
-      </c>
+      <c r="F33" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
+      <c r="I33" s="1">
+        <v>-1</v>
+      </c>
       <c r="J33" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>
       </c>
-      <c r="L33" s="1">
-        <v>1</v>
-      </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" spans="1:14">
+      <c r="L33" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="1:12">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>2017</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E34" s="1">
         <v>0</v>
       </c>
-      <c r="F34" s="1">
-        <v>0</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="F34" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
+      <c r="I34" s="1">
+        <v>-1</v>
+      </c>
       <c r="J34" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
       </c>
-      <c r="L34" s="1">
-        <v>1</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" spans="1:14">
+      <c r="L34" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="1:12">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>2018</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E35" s="1">
         <v>0</v>
       </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>118</v>
-      </c>
+      <c r="F35" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
+      <c r="I35" s="1">
+        <v>-1</v>
+      </c>
       <c r="J35" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
       </c>
-      <c r="L35" s="1">
-        <v>1</v>
-      </c>
-      <c r="M35" s="1">
-        <v>0</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" spans="1:14">
+      <c r="L35" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="1:12">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>2019</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E36" s="1">
         <v>0</v>
       </c>
-      <c r="F36" s="1">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>121</v>
-      </c>
+      <c r="F36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
+      <c r="I36" s="1">
+        <v>-1</v>
+      </c>
       <c r="J36" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
       </c>
-      <c r="L36" s="1">
-        <v>1</v>
-      </c>
-      <c r="M36" s="1">
-        <v>0</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" spans="1:14">
+      <c r="L36" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:12">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>2020</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E37" s="1">
         <v>0</v>
       </c>
-      <c r="F37" s="1">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>124</v>
-      </c>
+      <c r="F37" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
+      <c r="I37" s="1">
+        <v>-1</v>
+      </c>
       <c r="J37" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
         <v>0</v>
       </c>
-      <c r="L37" s="1">
-        <v>1</v>
-      </c>
-      <c r="M37" s="1">
-        <v>0</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" spans="1:14">
+      <c r="L37" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" spans="1:12">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>2021</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E38" s="1">
         <v>0</v>
       </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>127</v>
-      </c>
+      <c r="F38" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
+      <c r="I38" s="1">
+        <v>-1</v>
+      </c>
       <c r="J38" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
         <v>0</v>
       </c>
-      <c r="L38" s="1">
-        <v>1</v>
-      </c>
-      <c r="M38" s="1">
-        <v>0</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" spans="1:14">
+      <c r="L38" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:12">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>2022</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E39" s="1">
         <v>0</v>
       </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="F39" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+      <c r="I39" s="1">
+        <v>-1</v>
+      </c>
       <c r="J39" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
       </c>
-      <c r="L39" s="1">
-        <v>1</v>
-      </c>
-      <c r="M39" s="1">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" spans="1:14">
+      <c r="L39" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" spans="1:12">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>2023</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E40" s="1">
         <v>0</v>
       </c>
-      <c r="F40" s="1">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>133</v>
-      </c>
+      <c r="F40" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
+      <c r="I40" s="1">
+        <v>-1</v>
+      </c>
       <c r="J40" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
         <v>0</v>
       </c>
-      <c r="L40" s="1">
-        <v>1</v>
-      </c>
-      <c r="M40" s="1">
-        <v>0</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" spans="1:14">
+      <c r="L40" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" spans="1:12">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>2024</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
       </c>
-      <c r="F41" s="1">
-        <v>0</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>136</v>
-      </c>
+      <c r="F41" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="I41" s="1">
+        <v>-1</v>
+      </c>
       <c r="J41" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
         <v>0</v>
       </c>
-      <c r="L41" s="1">
-        <v>1</v>
-      </c>
-      <c r="M41" s="1">
-        <v>0</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" spans="1:14">
+      <c r="L41" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" spans="1:12">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>2025</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
       </c>
-      <c r="F42" s="1">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>139</v>
-      </c>
+      <c r="F42" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G42" s="2"/>
       <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="I42" s="1">
+        <v>-1</v>
+      </c>
       <c r="J42" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
         <v>0</v>
       </c>
-      <c r="L42" s="1">
-        <v>1</v>
-      </c>
-      <c r="M42" s="1">
-        <v>0</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" spans="1:14">
+      <c r="L42" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" spans="1:12">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>2026</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
       </c>
-      <c r="F43" s="1">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>142</v>
-      </c>
+      <c r="F43" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G43" s="2"/>
       <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="I43" s="1">
+        <v>-1</v>
+      </c>
       <c r="J43" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
         <v>0</v>
       </c>
-      <c r="L43" s="1">
-        <v>1</v>
-      </c>
-      <c r="M43" s="1">
-        <v>0</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>143</v>
+      <c r="L43" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SpecialEffectTable.xlsx
+++ b/AAAGameData/DataTables/SpecialEffectTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="208">
   <si>
     <t>#</t>
   </si>
@@ -440,100 +440,151 @@
     <t>{"triggerEvent":"OnDamageTaken","effect":"Reflect","ratio":0.15}</t>
   </si>
   <si>
+    <t>王者之击</t>
+  </si>
+  <si>
+    <t>普攻有15%概率造成额外50%真实伤害</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnAttack","chance":0.15,"effect":"TrueDamage","ratio":0.5}</t>
+  </si>
+  <si>
+    <t>龙血守护</t>
+  </si>
+  <si>
+    <t>受到致命伤害时免死一次并回复10%生命（每场战斗限1次）</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnLethalDamage","effect":"PreventDeath","healRatio":0.1,"maxTrigger":1}</t>
+  </si>
+  <si>
+    <t>灵动之风</t>
+  </si>
+  <si>
+    <t>每次攻击获得5%移速叠3层，满层时下次攻击必定暴击</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnAttack","effect":"StackSpeed","speedPerStack":0.05,"maxStack":3,"fullStackCrit":true}</t>
+  </si>
+  <si>
+    <t>月光护盾</t>
+  </si>
+  <si>
+    <t>受击时20%概率生成护盾（最大生命值10%，5秒）</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnDamageTaken","chance":0.2,"effect":"Shield","shieldRatio":0.1,"duration":5}</t>
+  </si>
+  <si>
+    <t>穿甲箭</t>
+  </si>
+  <si>
+    <t>攻击时25%概率无视目标50%防御</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnAttack","chance":0.25,"effect":"ArmorPenetration","ratio":0.5}</t>
+  </si>
+  <si>
+    <t>月华回复</t>
+  </si>
+  <si>
+    <t>每次攻击回复自身1%最大生命值</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnAttack","effect":"HealOnHit","healRatio":0.01}</t>
+  </si>
+  <si>
+    <t>噬魂</t>
+  </si>
+  <si>
+    <t>击杀敌人回复自身20%最大生命值</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnKill","effect":"HealOnKill","healRatio":0.2}</t>
+  </si>
+  <si>
+    <t>炎魔威压</t>
+  </si>
+  <si>
+    <t>战斗开始时给全体友方攻击+10%</t>
+  </si>
+  <si>
+    <t>{"BuffIds":[],"SelfBuffIds":[]}</t>
+  </si>
+  <si>
+    <t>燃烧之刃</t>
+  </si>
+  <si>
+    <t>攻击附带燃烧DOT（3秒，每秒攻击力20%火焰伤害）</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnAttack","effect":"BurnDot","duration":3,"damageRatio":0.2}</t>
+  </si>
+  <si>
+    <t>落樱斩</t>
+  </si>
+  <si>
+    <t>暴击时额外造成目标当前生命值5%的伤害</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnCrit","effect":"CurrentHpDamage","ratio":0.05}</t>
+  </si>
+  <si>
+    <t>暗影突袭</t>
+  </si>
+  <si>
+    <t>战斗开始时获得隐身3秒，首次攻击伤害+100%</t>
+  </si>
+  <si>
+    <t>圣光领域</t>
+  </si>
+  <si>
+    <t>每5秒回复自身3%最大生命值</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnInterval","interval":5,"effect":"HealSelf","healRatio":0.03}</t>
+  </si>
+  <si>
+    <t>嗜血狂热</t>
+  </si>
+  <si>
+    <t>击杀敌人后攻速+30%持续3秒</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnKill","effect":"AtkSpeedBuff","bonus":0.3,"duration":3}</t>
+  </si>
+  <si>
+    <t>霜冻步伐</t>
+  </si>
+  <si>
+    <t>普攻附带减速（降低目标20%移速，2秒）</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnAttack","effect":"Slow","slowRatio":0.2,"duration":2}</t>
+  </si>
+  <si>
+    <t>连锁闪电</t>
+  </si>
+  <si>
+    <t>每第3次攻击释放闪电，对附近敌人造成50%法术伤害</t>
+  </si>
+  <si>
+    <t>{"triggerEvent":"OnAttackCount","count":3,"effect":"ChainLightning","damageRatio":0.5}</t>
+  </si>
+  <si>
     <t>羁绊·三神器之力</t>
   </si>
   <si>
-    <t>集齐三神器，暴击伤害+50%</t>
+    <t>集齐三神器，全属性+20%，攻击时有20%概率造成三倍伤害</t>
   </si>
   <si>
     <t>{"SelfBuffIds":[7003]}</t>
   </si>
   <si>
-    <t>王者之击</t>
-  </si>
-  <si>
-    <t>普攻有15%概率造成额外50%真实伤害</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnAttack","chance":0.15,"effect":"TrueDamage","ratio":0.5}</t>
-  </si>
-  <si>
-    <t>龙血守护</t>
-  </si>
-  <si>
-    <t>受到致命伤害时免死一次并回复10%生命（每场战斗限1次）</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnLethalDamage","effect":"PreventDeath","healRatio":0.1,"maxTrigger":1}</t>
-  </si>
-  <si>
-    <t>灵动之风</t>
-  </si>
-  <si>
-    <t>每次攻击获得5%移速叠3层，满层时下次攻击必定暴击</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnAttack","effect":"StackSpeed","speedPerStack":0.05,"maxStack":3,"fullStackCrit":true}</t>
-  </si>
-  <si>
-    <t>月光护盾</t>
-  </si>
-  <si>
-    <t>受击时20%概率生成护盾（最大生命值10%，5秒）</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnDamageTaken","chance":0.2,"effect":"Shield","shieldRatio":0.1,"duration":5}</t>
-  </si>
-  <si>
-    <t>穿甲箭</t>
-  </si>
-  <si>
-    <t>攻击时25%概率无视目标50%防御</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnAttack","chance":0.25,"effect":"ArmorPenetration","ratio":0.5}</t>
-  </si>
-  <si>
-    <t>月华回复</t>
-  </si>
-  <si>
-    <t>每次攻击回复自身1%最大生命值</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnAttack","effect":"HealOnHit","healRatio":0.01}</t>
-  </si>
-  <si>
-    <t>噬魂</t>
-  </si>
-  <si>
-    <t>击杀敌人回复自身20%最大生命值</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnKill","effect":"HealOnKill","healRatio":0.2}</t>
-  </si>
-  <si>
-    <t>炎魔威压</t>
-  </si>
-  <si>
-    <t>战斗开始时给全体友方攻击+10%</t>
-  </si>
-  <si>
-    <t>{"BuffIds":[],"SelfBuffIds":[]}</t>
-  </si>
-  <si>
-    <t>燃烧之刃</t>
-  </si>
-  <si>
-    <t>攻击附带燃烧DOT（3秒，每秒攻击力20%火焰伤害）</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnAttack","effect":"BurnDot","duration":3,"damageRatio":0.2}</t>
-  </si>
-  <si>
     <t>羁绊·月神之力</t>
   </si>
   <si>
-    <t>集齐月神宝物，受伤-15%，魔抗+20%</t>
+    <t>集齐月神宝物，防御+30%，法术抗性+20%，生命恢复+5%</t>
   </si>
   <si>
     <t>{"SelfBuffIds":[7004]}</t>
@@ -542,63 +593,12 @@
     <t>羁绊·炎魔之怒</t>
   </si>
   <si>
-    <t>集齐炎魔宝物，攻击+20%，暴击率+15%</t>
+    <t>集齐炎魔宝物，攻击+30%，火伤害+50%，暴击率+15%</t>
   </si>
   <si>
     <t>{"SelfBuffIds":[7005]}</t>
   </si>
   <si>
-    <t>落樱斩</t>
-  </si>
-  <si>
-    <t>暴击时额外造成目标当前生命值5%的伤害</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnCrit","effect":"CurrentHpDamage","ratio":0.05}</t>
-  </si>
-  <si>
-    <t>暗影突袭</t>
-  </si>
-  <si>
-    <t>战斗开始时获得隐身3秒，首次攻击伤害+100%</t>
-  </si>
-  <si>
-    <t>圣光领域</t>
-  </si>
-  <si>
-    <t>每5秒回复自身3%最大生命值</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnInterval","interval":5,"effect":"HealSelf","healRatio":0.03}</t>
-  </si>
-  <si>
-    <t>嗜血狂热</t>
-  </si>
-  <si>
-    <t>击杀敌人后攻速+30%持续3秒</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnKill","effect":"AtkSpeedBuff","bonus":0.3,"duration":3}</t>
-  </si>
-  <si>
-    <t>霜冻步伐</t>
-  </si>
-  <si>
-    <t>普攻附带减速（降低目标20%移速，2秒）</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnAttack","effect":"Slow","slowRatio":0.2,"duration":2}</t>
-  </si>
-  <si>
-    <t>连锁闪电</t>
-  </si>
-  <si>
-    <t>每第3次攻击释放闪电，对附近敌人造成50%法术伤害</t>
-  </si>
-  <si>
-    <t>{"triggerEvent":"OnAttackCount","count":3,"effect":"ChainLightning","damageRatio":0.5}</t>
-  </si>
-  <si>
     <t>羁绊·日月之力</t>
   </si>
   <si>
@@ -615,6 +615,42 @@
   </si>
   <si>
     <t>{"SelfBuffIds":[7002]}</t>
+  </si>
+  <si>
+    <t>羁绊·污染生物之力</t>
+  </si>
+  <si>
+    <t>全体污染生物种族棋子获得伤害加深效果</t>
+  </si>
+  <si>
+    <t>{"SelfBuffIds":[7006]}</t>
+  </si>
+  <si>
+    <t>羁绊·灵魂之力</t>
+  </si>
+  <si>
+    <t>该棋子获得灵魂之力加成</t>
+  </si>
+  <si>
+    <t>{"SelfBuffIds":[7007]}</t>
+  </si>
+  <si>
+    <t>羁绊·战士之力</t>
+  </si>
+  <si>
+    <t>全体战士职业棋子攻击力+15%，护甲+10%</t>
+  </si>
+  <si>
+    <t>{"SelfBuffIds":[7008]}</t>
+  </si>
+  <si>
+    <t>羁绊·射手之力</t>
+  </si>
+  <si>
+    <t>该棋子攻击距离+2，攻击力+10%</t>
+  </si>
+  <si>
+    <t>{"SelfBuffIds":[7009]}</t>
   </si>
 </sst>
 </file>
@@ -1586,7 +1622,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1925,7 +1961,7 @@
     <row r="18" ht="15" customHeight="1" spans="1:7">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
-        <v>2001</v>
+        <v>1005</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
@@ -1944,7 +1980,7 @@
     <row r="19" ht="15" customHeight="1" spans="1:7">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
-        <v>2002</v>
+        <v>1006</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
@@ -1963,7 +1999,7 @@
     <row r="20" ht="15" customHeight="1" spans="1:7">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
-        <v>2003</v>
+        <v>1007</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
@@ -1982,7 +2018,7 @@
     <row r="21" ht="15" customHeight="1" spans="1:7">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
-        <v>2004</v>
+        <v>1008</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
@@ -2001,7 +2037,7 @@
     <row r="22" ht="15" customHeight="1" spans="1:7">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
-        <v>2005</v>
+        <v>1009</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
@@ -2020,7 +2056,7 @@
     <row r="23" ht="15" customHeight="1" spans="1:7">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
-        <v>2006</v>
+        <v>1010</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
@@ -2039,7 +2075,7 @@
     <row r="24" ht="15" customHeight="1" spans="1:7">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
-        <v>2007</v>
+        <v>1011</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
@@ -2058,7 +2094,7 @@
     <row r="25" ht="15" customHeight="1" spans="1:7">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
-        <v>2008</v>
+        <v>1012</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
@@ -2077,7 +2113,7 @@
     <row r="26" ht="15" customHeight="1" spans="1:7">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
-        <v>2009</v>
+        <v>1013</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
@@ -2096,7 +2132,7 @@
     <row r="27" ht="15" customHeight="1" spans="1:7">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
-        <v>2010</v>
+        <v>1014</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
@@ -2115,7 +2151,7 @@
     <row r="28" ht="15" customHeight="1" spans="1:7">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
-        <v>2011</v>
+        <v>1015</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
@@ -2134,7 +2170,7 @@
     <row r="29" ht="15" customHeight="1" spans="1:7">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
-        <v>2012</v>
+        <v>1016</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
@@ -2153,7 +2189,7 @@
     <row r="30" ht="15" customHeight="1" spans="1:7">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
-        <v>2013</v>
+        <v>1017</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
@@ -2172,7 +2208,7 @@
     <row r="31" ht="15" customHeight="1" spans="1:7">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
-        <v>2014</v>
+        <v>1018</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
@@ -2191,7 +2227,7 @@
     <row r="32" ht="15" customHeight="1" spans="1:7">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
-        <v>2015</v>
+        <v>1019</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
@@ -2210,7 +2246,7 @@
     <row r="33" ht="15" customHeight="1" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
-        <v>2016</v>
+        <v>1020</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
@@ -2229,7 +2265,7 @@
     <row r="34" ht="15" customHeight="1" spans="1:7">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
-        <v>2017</v>
+        <v>1021</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
@@ -2248,7 +2284,7 @@
     <row r="35" ht="15" customHeight="1" spans="1:7">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
-        <v>2018</v>
+        <v>1022</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
@@ -2267,7 +2303,7 @@
     <row r="36" ht="15" customHeight="1" spans="1:7">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
-        <v>2019</v>
+        <v>1023</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
@@ -2286,7 +2322,7 @@
     <row r="37" ht="15" customHeight="1" spans="1:7">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
-        <v>2020</v>
+        <v>1024</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
@@ -2305,7 +2341,7 @@
     <row r="38" ht="15" customHeight="1" spans="1:7">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
-        <v>2021</v>
+        <v>1025</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
@@ -2324,7 +2360,7 @@
     <row r="39" ht="15" customHeight="1" spans="1:7">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
-        <v>2022</v>
+        <v>1026</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
@@ -2343,7 +2379,7 @@
     <row r="40" ht="15" customHeight="1" spans="1:7">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
-        <v>2023</v>
+        <v>1027</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
@@ -2362,7 +2398,7 @@
     <row r="41" ht="15" customHeight="1" spans="1:7">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
-        <v>2024</v>
+        <v>1028</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
@@ -2381,7 +2417,7 @@
     <row r="42" ht="15" customHeight="1" spans="1:7">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
-        <v>2025</v>
+        <v>1029</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
@@ -2400,7 +2436,7 @@
     <row r="43" ht="15" customHeight="1" spans="1:7">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
-        <v>2026</v>
+        <v>1030</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
@@ -2476,14 +2512,14 @@
     <row r="47" ht="15" customHeight="1" spans="1:7">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
-        <v>3004</v>
+        <v>2007</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E47" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>138</v>
@@ -2495,7 +2531,7 @@
     <row r="48" ht="15" customHeight="1" spans="1:7">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
-        <v>4001</v>
+        <v>2008</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
@@ -2514,7 +2550,7 @@
     <row r="49" ht="15" customHeight="1" spans="1:7">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
-        <v>4002</v>
+        <v>2009</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
@@ -2533,7 +2569,7 @@
     <row r="50" ht="15" customHeight="1" spans="1:7">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
-        <v>4003</v>
+        <v>3004</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
@@ -2552,7 +2588,7 @@
     <row r="51" ht="15" customHeight="1" spans="1:7">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
-        <v>5001</v>
+        <v>3005</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
@@ -2571,7 +2607,7 @@
     <row r="52" ht="15" customHeight="1" spans="1:7">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
-        <v>5002</v>
+        <v>3006</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
@@ -2590,7 +2626,7 @@
     <row r="53" ht="15" customHeight="1" spans="1:7">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
-        <v>5003</v>
+        <v>3007</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
@@ -2609,14 +2645,14 @@
     <row r="54" ht="15" customHeight="1" spans="1:7">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
-        <v>5004</v>
+        <v>3008</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
         <v>158</v>
       </c>
       <c r="E54" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>159</v>
@@ -2628,14 +2664,14 @@
     <row r="55" ht="15" customHeight="1" spans="1:7">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
-        <v>5005</v>
+        <v>3009</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
         <v>161</v>
       </c>
       <c r="E55" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>162</v>
@@ -2647,7 +2683,7 @@
     <row r="56" ht="15" customHeight="1" spans="1:7">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
-        <v>5006</v>
+        <v>2001</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
@@ -2666,7 +2702,7 @@
     <row r="57" ht="15" customHeight="1" spans="1:7">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
-        <v>5101</v>
+        <v>2002</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1" t="s">
@@ -2679,70 +2715,70 @@
         <v>168</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:7">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
-        <v>5102</v>
+        <v>2003</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E58" s="1">
+        <v>4</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E58" s="1">
-        <v>2</v>
-      </c>
-      <c r="F58" s="1" t="s">
+      <c r="G58" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="1:7">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
-        <v>6001</v>
+        <v>2004</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E59" s="1">
         <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:7">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
-        <v>6002</v>
+        <v>2005</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E60" s="1">
+        <v>4</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E60" s="1">
-        <v>2</v>
-      </c>
-      <c r="F60" s="1" t="s">
+      <c r="G60" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:7">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
-        <v>6003</v>
+        <v>2006</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1" t="s">
@@ -2761,14 +2797,14 @@
     <row r="62" ht="15" customHeight="1" spans="1:7">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
-        <v>6004</v>
+        <v>4001</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1" t="s">
         <v>181</v>
       </c>
       <c r="E62" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>182</v>
@@ -2780,14 +2816,14 @@
     <row r="63" ht="15" customHeight="1" spans="1:7">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
-        <v>6005</v>
+        <v>4002</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1" t="s">
         <v>184</v>
       </c>
       <c r="E63" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>185</v>
@@ -2799,14 +2835,14 @@
     <row r="64" ht="15" customHeight="1" spans="1:7">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
-        <v>6006</v>
+        <v>4003</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1" t="s">
         <v>187</v>
       </c>
       <c r="E64" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>188</v>
@@ -2818,7 +2854,7 @@
     <row r="65" ht="15" customHeight="1" spans="1:7">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
-        <v>7001</v>
+        <v>4004</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1" t="s">
@@ -2837,7 +2873,7 @@
     <row r="66" ht="15" customHeight="1" spans="1:7">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
-        <v>7002</v>
+        <v>4005</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1" t="s">
@@ -2851,6 +2887,82 @@
       </c>
       <c r="G66" s="1" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" spans="1:7">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1">
+        <v>4006</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E67" s="1">
+        <v>2</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1" spans="1:7">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1">
+        <v>4007</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E68" s="1">
+        <v>2</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" spans="1:7">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1">
+        <v>4008</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E69" s="1">
+        <v>2</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" spans="1:7">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1">
+        <v>4009</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E70" s="1">
+        <v>2</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SpecialEffectTable.xlsx
+++ b/AAAGameData/DataTables/SpecialEffectTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="205">
   <si>
     <t>#</t>
   </si>
@@ -395,22 +395,13 @@
     <t>{"type":"UnlockCard","cardId":1024}</t>
   </si>
   <si>
-    <t>解锁伤害转移</t>
-  </si>
-  <si>
-    <t>使用后解锁策略卡：伤害转移</t>
+    <t>解锁绝对零度</t>
+  </si>
+  <si>
+    <t>使用后解锁策略卡：绝对零度</t>
   </si>
   <si>
     <t>{"type":"UnlockCard","cardId":1025}</t>
-  </si>
-  <si>
-    <t>解锁绝对零度</t>
-  </si>
-  <si>
-    <t>使用后解锁策略卡：绝对零度</t>
-  </si>
-  <si>
-    <t>{"type":"UnlockCard","cardId":1026}</t>
   </si>
   <si>
     <t>神佑之力</t>
@@ -663,14 +654,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1126,148 +1110,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1622,8 +1606,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:G69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2436,14 +2420,14 @@
     <row r="43" ht="15" customHeight="1" spans="1:7">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
-        <v>1030</v>
+        <v>3001</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
         <v>125</v>
       </c>
       <c r="E43" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>126</v>
@@ -2455,7 +2439,7 @@
     <row r="44" ht="15" customHeight="1" spans="1:7">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
@@ -2474,7 +2458,7 @@
     <row r="45" ht="15" customHeight="1" spans="1:7">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
@@ -2493,7 +2477,7 @@
     <row r="46" ht="15" customHeight="1" spans="1:7">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
-        <v>3003</v>
+        <v>2007</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
@@ -2512,7 +2496,7 @@
     <row r="47" ht="15" customHeight="1" spans="1:7">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
@@ -2531,7 +2515,7 @@
     <row r="48" ht="15" customHeight="1" spans="1:7">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
@@ -2550,7 +2534,7 @@
     <row r="49" ht="15" customHeight="1" spans="1:7">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
-        <v>2009</v>
+        <v>3004</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
@@ -2569,7 +2553,7 @@
     <row r="50" ht="15" customHeight="1" spans="1:7">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
@@ -2588,7 +2572,7 @@
     <row r="51" ht="15" customHeight="1" spans="1:7">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
@@ -2607,7 +2591,7 @@
     <row r="52" ht="15" customHeight="1" spans="1:7">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
@@ -2626,14 +2610,14 @@
     <row r="53" ht="15" customHeight="1" spans="1:7">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
         <v>155</v>
       </c>
       <c r="E53" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>156</v>
@@ -2645,14 +2629,14 @@
     <row r="54" ht="15" customHeight="1" spans="1:7">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
         <v>158</v>
       </c>
       <c r="E54" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>159</v>
@@ -2664,7 +2648,7 @@
     <row r="55" ht="15" customHeight="1" spans="1:7">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
-        <v>3009</v>
+        <v>2001</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
@@ -2683,45 +2667,45 @@
     <row r="56" ht="15" customHeight="1" spans="1:7">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
         <v>164</v>
       </c>
       <c r="E56" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>165</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:7">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E57" s="1">
+        <v>4</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E57" s="1">
-        <v>2</v>
-      </c>
-      <c r="F57" s="1" t="s">
+      <c r="G57" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:7">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
@@ -2740,7 +2724,7 @@
     <row r="59" ht="15" customHeight="1" spans="1:7">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
@@ -2759,7 +2743,7 @@
     <row r="60" ht="15" customHeight="1" spans="1:7">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
@@ -2778,14 +2762,14 @@
     <row r="61" ht="15" customHeight="1" spans="1:7">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
-        <v>2006</v>
+        <v>4001</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1" t="s">
         <v>178</v>
       </c>
       <c r="E61" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>179</v>
@@ -2797,7 +2781,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:7">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1" t="s">
@@ -2816,7 +2800,7 @@
     <row r="63" ht="15" customHeight="1" spans="1:7">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1" t="s">
@@ -2835,7 +2819,7 @@
     <row r="64" ht="15" customHeight="1" spans="1:7">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
-        <v>4003</v>
+        <v>4004</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1" t="s">
@@ -2854,7 +2838,7 @@
     <row r="65" ht="15" customHeight="1" spans="1:7">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1" t="s">
@@ -2873,7 +2857,7 @@
     <row r="66" ht="15" customHeight="1" spans="1:7">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1" t="s">
@@ -2892,7 +2876,7 @@
     <row r="67" ht="15" customHeight="1" spans="1:7">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1" t="s">
@@ -2911,7 +2895,7 @@
     <row r="68" ht="15" customHeight="1" spans="1:7">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
-        <v>4007</v>
+        <v>4008</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1" t="s">
@@ -2930,7 +2914,7 @@
     <row r="69" ht="15" customHeight="1" spans="1:7">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
-        <v>4008</v>
+        <v>4009</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1" t="s">
@@ -2944,25 +2928,6 @@
       </c>
       <c r="G69" s="1" t="s">
         <v>204</v>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" spans="1:7">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1">
-        <v>4009</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E70" s="1">
-        <v>2</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
   </sheetData>
